--- a/InputData/trans/VRSbRIC/Veh Revenue Share by Recipient ISIC Code.xlsx
+++ b/InputData/trans/VRSbRIC/Veh Revenue Share by Recipient ISIC Code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\VRSbRIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/khushi_parakh_wri_org/Documents/Desktop/EPS update/current WIP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFABE065-4FE4-4AA3-B341-5EF8B4091819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{EFABE065-4FE4-4AA3-B341-5EF8B4091819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EED8EBDB-7D14-4AEC-BE62-78EE49F67D34}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{98104574-AC6C-45D3-B7DA-9D389A9BFE72}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{98104574-AC6C-45D3-B7DA-9D389A9BFE72}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -619,9 +619,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -659,7 +659,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -765,7 +765,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -907,7 +907,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -916,17 +916,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6E6C8E-C26C-4C73-93CC-7550EEEA6E9A}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -934,62 +934,62 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="3">
         <v>2009</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="3">
         <v>2010</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>123</v>
       </c>
@@ -997,7 +997,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>125</v>
       </c>
@@ -1014,14 +1014,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFD20EDD-472C-457D-96DA-E16DAC72FCB8}">
   <dimension ref="A1:E66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.7265625" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>1.4600000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>70</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>75</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>77</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>85</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>86</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>88</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>90</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>92</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>93</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>95</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>97</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>98</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>99</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>100</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>101</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>102</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>103</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>104</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>105</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>106</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>107</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>108</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>109</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>110</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -1622,14 +1622,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{289C64CC-E62D-4411-9368-8E9242EA44DA}">
   <dimension ref="A1:E66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.7265625" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>1.3600000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>70</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>75</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>77</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>85</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>86</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>88</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>90</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>92</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>93</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>95</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>97</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>98</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>99</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>100</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>101</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>102</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>103</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>104</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>105</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>106</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>107</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>108</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>109</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>110</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -2233,12 +2233,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AQ7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>112</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>113</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>114</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>115</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C3:AQ7" si="1">C3</f>
+        <f t="shared" ref="C4:AQ7" si="1">C3</f>
         <v>0</v>
       </c>
       <c r="D4">
@@ -2887,7 +2887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>117</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>118</v>
       </c>
@@ -3406,4 +3406,198 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6D91731-E6F1-4F30-97AE-27DDE4A4241F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B893343C-FD2B-4158-86D2-6B6548535644}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90D78269-D77A-4BB7-B972-161910D2207F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>